--- a/Gateway_AI_CBA_ROI_v2_10.xlsx
+++ b/Gateway_AI_CBA_ROI_v2_10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d1bd2bd6a12f2630/AI ML Mini Projects/CBA_ROI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{EFEE8BC3-4FAF-4B9D-9D56-92059780D303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="14_{EFEE8BC3-4FAF-4B9D-9D56-92059780D303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{374DC808-FAD9-4DFD-A813-273C1AAB2F39}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CBA &amp; ROI Dashboard" sheetId="1" r:id="rId1"/>
@@ -467,46 +467,12 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="15" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -554,9 +520,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -585,6 +548,43 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="15" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -853,7 +853,7 @@
   <dimension ref="A1:F44"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="1" max="1" width="54.7109375" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
@@ -861,587 +861,587 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
     </row>
     <row r="2" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
     </row>
     <row r="3" spans="1:6" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
     </row>
     <row r="5" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
     </row>
     <row r="6" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="5">
         <v>4</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
     </row>
     <row r="7" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="5">
         <v>65</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
     </row>
     <row r="8" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="5">
         <v>7</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
     </row>
     <row r="9" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="5">
         <v>48</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
     </row>
     <row r="10" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
     </row>
     <row r="11" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="5">
         <v>8500</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
     </row>
     <row r="12" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="5">
         <v>320</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
     </row>
     <row r="13" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="5">
         <v>1200</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
     </row>
     <row r="14" spans="1:6" ht="9.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="15" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
     </row>
     <row r="16" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="15" t="s">
+      <c r="B16" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="E16" s="3" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="7">
         <f>B6*B8*B9*B7</f>
         <v>87360</v>
       </c>
-      <c r="C17" s="19">
+      <c r="C17" s="7">
         <f>B17*(1-B10)</f>
         <v>13104.000000000002</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="7">
         <f>B17-C17</f>
         <v>74256</v>
       </c>
-      <c r="E17" s="20">
+      <c r="E17" s="8">
         <f>IF(B17=0,0,-D17/B17)</f>
         <v>-0.85</v>
       </c>
-      <c r="F17" s="21"/>
+      <c r="F17" s="9"/>
     </row>
     <row r="18" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="23">
+      <c r="B18" s="11">
         <v>0</v>
       </c>
-      <c r="C18" s="23">
+      <c r="C18" s="11">
         <f>B13*B10</f>
         <v>1020</v>
       </c>
-      <c r="D18" s="23">
+      <c r="D18" s="11">
         <f>-C19</f>
         <v>0</v>
       </c>
-      <c r="E18" s="24"/>
+      <c r="E18" s="12"/>
     </row>
     <row r="19" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="19">
+      <c r="B19" s="7">
         <v>0</v>
       </c>
-      <c r="C19" s="19">
+      <c r="C19" s="7">
         <f>B14/3</f>
         <v>0</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="7">
         <f>-C19</f>
         <v>0</v>
       </c>
-      <c r="E19" s="20"/>
+      <c r="E19" s="8"/>
     </row>
     <row r="20" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="25" t="s">
+      <c r="A20" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="14">
         <f>B17+B18+B19</f>
         <v>87360</v>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="14">
         <f>C17+C18+C19</f>
         <v>14124.000000000002</v>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="14">
         <f>B20-C20</f>
         <v>73236</v>
       </c>
-      <c r="E20" s="27" t="str">
+      <c r="E20" s="15" t="str">
         <f>IF(B21=0,"-",-D21/B21)</f>
         <v>-</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
     </row>
     <row r="22" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
+      <c r="A22" s="31"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
     </row>
     <row r="23" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
+      <c r="B23" s="32"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="32"/>
     </row>
     <row r="24" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B24" s="15" t="s">
+      <c r="B24" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="28" t="s">
+      <c r="B25" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D25" s="30">
+      <c r="D25" s="18">
         <f>B6*B8*B9*B10*B7</f>
         <v>74255.999999999985</v>
       </c>
-      <c r="E25" s="31" t="s">
+      <c r="E25" s="19" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="18" t="s">
+      <c r="A26" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="32" t="s">
+      <c r="B26" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C26" s="33" t="s">
+      <c r="C26" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D26" s="34">
+      <c r="D26" s="21">
         <v>18200</v>
       </c>
-      <c r="E26" s="31" t="s">
+      <c r="E26" s="19" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="22" t="s">
+      <c r="A27" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B27" s="28" t="s">
+      <c r="B27" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="18">
         <v>9600</v>
       </c>
-      <c r="E27" s="35" t="s">
+      <c r="E27" s="22" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="18" t="s">
+      <c r="A28" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="34">
+      <c r="C28" s="37"/>
+      <c r="D28" s="21">
         <v>24000</v>
       </c>
-      <c r="E28" s="35" t="s">
+      <c r="E28" s="22" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="36" t="s">
+      <c r="A29" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="B29" s="37"/>
-      <c r="C29" s="38"/>
-      <c r="D29" s="39">
+      <c r="B29" s="24"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="26">
         <f>SUM(D25:D28)</f>
         <v>126055.99999999999</v>
       </c>
-      <c r="E29" s="31"/>
-      <c r="F29" s="38"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="25"/>
     </row>
     <row r="30" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
+      <c r="A30" s="31"/>
+      <c r="B30" s="31"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="31"/>
     </row>
     <row r="31" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
+      <c r="B31" s="32"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="32"/>
     </row>
     <row r="32" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="40" t="s">
+      <c r="A32" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="B32" s="6">
+      <c r="B32" s="33">
         <f>B11+B13</f>
         <v>9700</v>
       </c>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
     </row>
     <row r="33" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="40" t="s">
+      <c r="A33" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="B33" s="6">
+      <c r="B33" s="33">
         <f>B12*12</f>
         <v>3840</v>
       </c>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="33"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
     </row>
     <row r="34" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="40" t="s">
+      <c r="A34" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B34" s="34">
         <f>D29</f>
         <v>126055.99999999999</v>
       </c>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
     </row>
     <row r="35" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="40" t="s">
+      <c r="A35" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="B35" s="5">
+      <c r="B35" s="34">
         <f>B34-B33</f>
         <v>122215.99999999999</v>
       </c>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
     </row>
     <row r="36" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="40" t="s">
+      <c r="A36" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36" s="35">
         <f>IF(B34=0,"N/A",B32/B35*12)</f>
         <v>0.95241212279897902</v>
       </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
+      <c r="C36" s="35"/>
+      <c r="D36" s="35"/>
+      <c r="E36" s="35"/>
+      <c r="F36" s="35"/>
     </row>
     <row r="37" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="40" t="s">
+      <c r="A37" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B37" s="36">
         <f>IF(B32=0,"N/A",(B35*3-B32)/B32)</f>
         <v>36.798762886597935</v>
       </c>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
+      <c r="C37" s="36"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="36"/>
+      <c r="F37" s="36"/>
     </row>
     <row r="38" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="41" t="s">
+      <c r="A38" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B38" s="30">
         <f>B35*3-B32</f>
         <v>356947.99999999994</v>
       </c>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
+      <c r="C38" s="30"/>
+      <c r="D38" s="30"/>
+      <c r="E38" s="30"/>
+      <c r="F38" s="30"/>
     </row>
     <row r="39" spans="1:6" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="8"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
+      <c r="A39" s="31"/>
+      <c r="B39" s="31"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="31"/>
     </row>
     <row r="40" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="12" t="s">
+      <c r="A40" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
+      <c r="B40" s="32"/>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32"/>
+      <c r="F40" s="32"/>
     </row>
     <row r="41" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
+      <c r="B41" s="29"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="29"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="29"/>
     </row>
     <row r="42" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
+      <c r="B42" s="29"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
     </row>
     <row r="43" spans="1:6" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
+      <c r="B43" s="29"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="29"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
     </row>
     <row r="44" spans="1:6" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="42" t="s">
+      <c r="A44" s="1" t="s">
         <v>66</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
     <mergeCell ref="A43:F43"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="A39:F39"/>
     <mergeCell ref="A40:F40"/>
     <mergeCell ref="A41:F41"/>
     <mergeCell ref="A42:F42"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
